--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACE\QUIZ_APP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RAI\quiz_Rai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC040EB-B4C8-489B-8E73-C8BBDD8113BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22935" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="TEST 1" sheetId="1" r:id="rId1"/>
@@ -19,6 +18,7 @@
     <sheet name="TEST 4" sheetId="4" r:id="rId4"/>
     <sheet name="TEST 5" sheetId="5" r:id="rId5"/>
     <sheet name="TEST 6" sheetId="6" r:id="rId6"/>
+    <sheet name="easy_set" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="64">
   <si>
     <t>Question</t>
   </si>
@@ -198,12 +198,36 @@
   </si>
   <si>
     <t>What is 5 - 2 ?</t>
+  </si>
+  <si>
+    <t>What is 1 + 1?</t>
+  </si>
+  <si>
+    <t>How many fingers do you have on one hand?</t>
+  </si>
+  <si>
+    <t>If you have 2 apples and eat 1, how many apples are left?</t>
+  </si>
+  <si>
+    <t>How many toes do you have?</t>
+  </si>
+  <si>
+    <t>What comes after 1?</t>
+  </si>
+  <si>
+    <t>If you have 3 cookies and give away 1, how many cookies are left?</t>
+  </si>
+  <si>
+    <t>How many balls are in a pair?</t>
+  </si>
+  <si>
+    <t>How many eyes do you see on your face?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -541,14 +565,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,7 +580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>45</v>
       </c>
@@ -564,7 +588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>46</v>
       </c>
@@ -572,7 +596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -580,7 +604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
@@ -588,7 +612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
@@ -596,7 +620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -604,7 +628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
@@ -612,7 +636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
@@ -620,7 +644,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>51</v>
       </c>
@@ -628,7 +652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
@@ -636,35 +660,35 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
     </row>
@@ -674,14 +698,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3B1B0B-5CBD-4DDC-AF2C-54DCB728EF7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -689,7 +713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -697,7 +721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -705,7 +729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -713,7 +737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -721,7 +745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -729,7 +753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -737,7 +761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -745,7 +769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -753,7 +777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -761,7 +785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -775,14 +799,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C199E01-FAD6-4EE3-9117-6AD93C423991}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -798,7 +822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -806,7 +830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -814,7 +838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -822,7 +846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -830,7 +854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -838,7 +862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -846,7 +870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -854,7 +878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -862,7 +886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -876,14 +900,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFBAD45-D0C6-4C3F-B64F-9431ECC3ED5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -891,7 +915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -899,7 +923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -907,7 +931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -915,7 +939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -923,7 +947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -931,7 +955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -939,7 +963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
@@ -947,7 +971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
@@ -955,7 +979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -963,7 +987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>33</v>
       </c>
@@ -971,7 +995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
@@ -985,14 +1009,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F5467A-3AB0-4590-AA86-B17EA6D49D84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -1008,7 +1032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
@@ -1016,7 +1040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1024,7 +1048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
@@ -1032,7 +1056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -1040,7 +1064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -1048,7 +1072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -1056,7 +1080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
@@ -1064,7 +1088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1072,7 +1096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
@@ -1086,14 +1110,14 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160A62C-5AAD-4616-A3EF-77631848BCD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1101,7 +1125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>54</v>
       </c>
@@ -1109,7 +1133,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
@@ -1117,7 +1141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>53</v>
       </c>
@@ -1125,7 +1149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1133,29 +1157,130 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="60.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="22935" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="22935" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="TEST1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
   <si>
     <t>Question</t>
   </si>
@@ -35,58 +35,127 @@
     <t>Answer</t>
   </si>
   <si>
-    <t>Are you an ambitious person?</t>
-  </si>
-  <si>
-    <t>Do you consider yourself forceful?</t>
-  </si>
-  <si>
-    <t>Are you a decisive person?</t>
-  </si>
-  <si>
-    <t>Do you prefer being direct in your communication?</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
-    <t>Are you an expressive person?</t>
-  </si>
-  <si>
-    <t>Are you enthusiastic?</t>
-  </si>
-  <si>
-    <t>Do you consider yourself friendly?</t>
-  </si>
-  <si>
-    <t>Are you demonstrative in your feelings?</t>
-  </si>
-  <si>
-    <t>Are you a methodical person?</t>
-  </si>
-  <si>
-    <t>Do you approach things systematically?</t>
-  </si>
-  <si>
-    <t>Are you reliable?</t>
-  </si>
-  <si>
-    <t>Do you consider yourself steady?</t>
-  </si>
-  <si>
-    <t>Are you an analytical person?</t>
-  </si>
-  <si>
-    <t>Do you consider yourself contemplative?</t>
-  </si>
-  <si>
-    <t>Are you conservative in your views?</t>
-  </si>
-  <si>
-    <t>Are you exacting in your work?</t>
-  </si>
-  <si>
-    <t>Are you a careful person?</t>
+    <t>Do you enjoy solving complex problems or puzzles?</t>
+  </si>
+  <si>
+    <t>Are you interested in working with computers and technology?</t>
+  </si>
+  <si>
+    <t>Do you like helping others learn new things?</t>
+  </si>
+  <si>
+    <t>Do you enjoy creating artistic or visual content?</t>
+  </si>
+  <si>
+    <t>Do you prefer working with data and numbers?</t>
+  </si>
+  <si>
+    <t>Are you interested in understanding how things work?</t>
+  </si>
+  <si>
+    <t>Do you enjoy organizing and planning events?</t>
+  </si>
+  <si>
+    <t>Are you interested in scientific research and experiments?</t>
+  </si>
+  <si>
+    <t>Do you like working on hands-on projects?</t>
+  </si>
+  <si>
+    <t>Do you enjoy writing and communication?</t>
+  </si>
+  <si>
+    <t>Are you good at explaining complex ideas to others?</t>
+  </si>
+  <si>
+    <t>Do you excel at analyzing data and finding patterns?</t>
+  </si>
+  <si>
+    <t>Are you skilled at resolving conflicts between people?</t>
+  </si>
+  <si>
+    <t>Can you easily learn new software or technical tools?</t>
+  </si>
+  <si>
+    <t>Are you good at managing multiple tasks simultaneously?</t>
+  </si>
+  <si>
+    <t>Do you have strong attention to detail?</t>
+  </si>
+  <si>
+    <t>Are you effective at leading team projects?</t>
+  </si>
+  <si>
+    <t>Can you quickly adapt to new situations?</t>
+  </si>
+  <si>
+    <t>Are you good at creative problem-solving?</t>
+  </si>
+  <si>
+    <t>Do you work well under pressure?</t>
+  </si>
+  <si>
+    <t>Do you aspire to start your own business?</t>
+  </si>
+  <si>
+    <t>Are you interested in working internationally?</t>
+  </si>
+  <si>
+    <t>Do you want to make a significant social impact through your work?</t>
+  </si>
+  <si>
+    <t>Is achieving a leadership position important to you?</t>
+  </si>
+  <si>
+    <t>Do you aim to be an expert in your field?</t>
+  </si>
+  <si>
+    <t>Are you interested in continuous learning and skill development?</t>
+  </si>
+  <si>
+    <t>Do you want to work on innovative or cutting-edge projects?</t>
+  </si>
+  <si>
+    <t>Is work-life balance a priority for your career?</t>
+  </si>
+  <si>
+    <t>Do you want to mentor others in your field?</t>
+  </si>
+  <si>
+    <t>Are you interested in working on global challenges?</t>
+  </si>
+  <si>
+    <t>Is working in an ethical environment important to you?</t>
+  </si>
+  <si>
+    <t>Do you value creativity and innovation in your work?</t>
+  </si>
+  <si>
+    <t>Is financial stability a key factor in your career choices?</t>
+  </si>
+  <si>
+    <t>Do you prefer working independently?</t>
+  </si>
+  <si>
+    <t>Is making a positive impact on society important to you?</t>
+  </si>
+  <si>
+    <t>Do you value recognition and awards in your work?</t>
+  </si>
+  <si>
+    <t>Is working in a diverse environment important to you?</t>
+  </si>
+  <si>
+    <t>Do you prefer structured and stable work environments?</t>
+  </si>
+  <si>
+    <t>Is intellectual challenge important in your work?</t>
+  </si>
+  <si>
+    <t>Do you value opportunities for rapid career advancement?</t>
   </si>
 </sst>
 </file>
@@ -431,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" bestFit="1" customWidth="1"/>
@@ -447,34 +516,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -484,7 +601,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" bestFit="1" customWidth="1"/>
@@ -500,34 +617,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" bestFit="1" customWidth="1"/>
@@ -553,34 +718,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +803,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" bestFit="1" customWidth="1"/>
@@ -606,42 +819,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
